--- a/pregenereated_results/s2/att_evalue_survey.xlsx
+++ b/pregenereated_results/s2/att_evalue_survey.xlsx
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.499321025741697</v>
+        <v>0.4993210257416965</v>
       </c>
       <c r="D2" t="n">
-        <v>1.575199818981438</v>
+        <v>1.575199818981437</v>
       </c>
       <c r="E2" t="n">
-        <v>2.527068849225471</v>
+        <v>2.527068849225469</v>
       </c>
       <c r="F2" t="n">
-        <v>2.071911862906454</v>
+        <v>2.071911862906451</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.216315028048566e-31</v>
+        <v>4.216315028059068e-31</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.04256676218162161</v>
+        <v>-0.04256676218162209</v>
       </c>
       <c r="D3" t="n">
         <v>1.039495764326114</v>
       </c>
       <c r="E3" t="n">
-        <v>1.242117776274021</v>
+        <v>1.242117776274022</v>
       </c>
       <c r="F3" t="n">
-        <v>1.480806964352345</v>
+        <v>1.480806964352357</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.2414710814149033</v>
+        <v>0.2414710814149321</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -572,16 +572,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.2951129364911815</v>
+        <v>0.295112936491181</v>
       </c>
       <c r="D4" t="n">
         <v>1.308070004950221</v>
       </c>
       <c r="E4" t="n">
-        <v>1.942874804002852</v>
+        <v>1.942874804002851</v>
       </c>
       <c r="F4" t="n">
-        <v>1.646301908670693</v>
+        <v>1.64630190867069</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>9.590676754537563e-12</v>
+        <v>9.590676754544794e-12</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
